--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -63,16 +68,16 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -221,12 +226,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -547,7 +558,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -571,16 +582,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
@@ -589,85 +600,85 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -675,10 +686,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -734,6 +745,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="004F81BD"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -995,13 +1011,10 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="12.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="37.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="45.2727272727273" customWidth="1"/>
+    <col min="1" max="161" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
